--- a/src/main/resources/2012/01/Nowak_Piotr.xlsx
+++ b/src/main/resources/2012/01/Nowak_Piotr.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t xml:space="preserve">Data</t>
   </si>
@@ -37,28 +37,22 @@
     <t xml:space="preserve">Podsumowanie spotkania</t>
   </si>
   <si>
-    <t xml:space="preserve">Ocena wymagan przygotowanych przez Janka</t>
+    <t xml:space="preserve">Ocena kodu</t>
   </si>
   <si>
     <t xml:space="preserve">Prezentacja dla klienta</t>
   </si>
   <si>
-    <t xml:space="preserve">Spotkanie po prezentacji, podsumowanie i wnioski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projekt architektury </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Przygotowanie do testów Erlanga - srodowisko</t>
+    <t xml:space="preserve">Mycie podłogi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poważne zadanie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noszenie cegieł</t>
   </si>
   <si>
     <t xml:space="preserve">Zabawa Erlangiem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testowanie Erlanga na potrzeby architektury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pierwszy prototyp technologiczny w Erlangu</t>
   </si>
 </sst>
 </file>
@@ -75,6 +69,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -97,12 +92,14 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -147,24 +144,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -294,128 +295,128 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="9.13671875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="60.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="60.85"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>40921</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>40922</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>40926</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>40931</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>40932</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>40933</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>40934</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>40934</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>40935</v>
       </c>
-      <c r="B10" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="0" t="n">
+      <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="C10" s="1" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>40938</v>
       </c>
-      <c r="B11" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="0" t="n">
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1" t="n">
         <v>8</v>
       </c>
     </row>
